--- a/jogos_2024-09-12.xlsx
+++ b/jogos_2024-09-12.xlsx
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD7" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2</v>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '46']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['18', '48']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45547.54166666666</v>
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1443,28 +1443,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T8" t="n">
         <v>2.75</v>
@@ -1473,53 +1473,53 @@
         <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="X8" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['12', '52']</t>
+          <t>['14', '51']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '62', '63', '73', '90+2']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45547.54166666666</v>
@@ -1536,35 +1536,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.83</v>
       </c>
       <c r="M9" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.7</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>3.28</v>
+        <v>3.64</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['63', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '29', '45', '46', '71', '87']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.15</v>
+        <v>2.6</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45547.54166666666</v>
@@ -1665,35 +1665,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>7.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
-        <v>3.64</v>
+        <v>3.28</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
       <c r="AA10" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['63', '89']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['6', '29', '45', '46', '71', '87']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>2.6</v>
+        <v>4.15</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45547.54166666666</v>
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>2.75</v>
@@ -1860,53 +1860,53 @@
         <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="X11" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2</v>
       </c>
-      <c r="Z11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['14', '51']</t>
+          <t>['12', '52']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['49', '62', '63', '73', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45547.54166666666</v>
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1.95</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['2', '46']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['18', '48']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45547.54166666666</v>
